--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.75824</v>
+        <v>16.6459</v>
       </c>
       <c r="D2" t="n">
-        <v>16.71766</v>
+        <v>16.46714</v>
       </c>
       <c r="E2" t="n">
-        <v>16.90632</v>
+        <v>16.55776</v>
       </c>
       <c r="F2" t="n">
-        <v>42.6059</v>
+        <v>41.8409</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05062</v>
+        <v>0.04997</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7877</v>
+        <v>1.83488</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.9003</v>
+        <v>16.76985</v>
       </c>
       <c r="D3" t="n">
-        <v>16.81775</v>
+        <v>16.32019</v>
       </c>
       <c r="E3" t="n">
-        <v>16.47658</v>
+        <v>16.58821</v>
       </c>
       <c r="F3" t="n">
-        <v>42.12505</v>
+        <v>42.2744</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04942</v>
+        <v>0.04875</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81745</v>
+        <v>1.81324</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.41365</v>
+        <v>17.0481</v>
       </c>
       <c r="D4" t="n">
-        <v>16.51832</v>
+        <v>16.07204</v>
       </c>
       <c r="E4" t="n">
-        <v>16.7126</v>
+        <v>16.34555</v>
       </c>
       <c r="F4" t="n">
-        <v>42.79923</v>
+        <v>42.04659</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05084</v>
+        <v>0.0503</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83354</v>
+        <v>1.82918</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.88973</v>
+        <v>16.45559</v>
       </c>
       <c r="D6" t="n">
-        <v>15.92042</v>
+        <v>16.07707</v>
       </c>
       <c r="E6" t="n">
-        <v>16.25176</v>
+        <v>16.08285</v>
       </c>
       <c r="F6" t="n">
-        <v>21.61333</v>
+        <v>21.68255</v>
       </c>
       <c r="G6" t="n">
-        <v>34.35158</v>
+        <v>33.63771</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.61403</v>
+        <v>16.64273</v>
       </c>
       <c r="D7" t="n">
-        <v>15.73222</v>
+        <v>16.02317</v>
       </c>
       <c r="E7" t="n">
-        <v>16.58911</v>
+        <v>16.19274</v>
       </c>
       <c r="F7" t="n">
-        <v>21.65683</v>
+        <v>21.29252</v>
       </c>
       <c r="G7" t="n">
-        <v>34.09169</v>
+        <v>33.85855</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.40428</v>
+        <v>16.46427</v>
       </c>
       <c r="D8" t="n">
-        <v>15.92984</v>
+        <v>16.0279</v>
       </c>
       <c r="E8" t="n">
-        <v>16.07716</v>
+        <v>16.34587</v>
       </c>
       <c r="F8" t="n">
-        <v>21.27815</v>
+        <v>21.40932</v>
       </c>
       <c r="G8" t="n">
-        <v>33.99776</v>
+        <v>34.31142</v>
       </c>
     </row>
   </sheetData>
